--- a/data/trans_orig/IP3108-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP3108-Edad-trans_orig.xlsx
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>630</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>6165</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60450</t>
+          <t>60518</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64847</t>
+          <t>64842</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65721</t>
+          <t>66379</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73488</t>
+          <t>73448</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>129461</t>
+          <t>129094</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>137702</t>
+          <t>137476</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7610</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2416</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>703</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14146</t>
+          <t>14786</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12166</t>
+          <t>12135</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9725</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22341</t>
+          <t>22666</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>13464</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>17339</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>220321</t>
+          <t>219550</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>234093</t>
+          <t>234322</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>231524</t>
+          <t>231410</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>243644</t>
+          <t>243185</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>456187</t>
+          <t>456860</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>475121</t>
+          <t>475535</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,28%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7797</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>706</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>8759</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>9865</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2705</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10590</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>6970</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17604</t>
+          <t>17957</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13367</t>
+          <t>12842</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>104543</t>
+          <t>104888</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>115259</t>
+          <t>115479</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>117863</t>
+          <t>118009</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>129642</t>
+          <t>129345</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>225802</t>
+          <t>224334</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>241366</t>
+          <t>241765</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10508</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>9668</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17136</t>
+          <t>16745</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11997</t>
+          <t>12689</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>13499</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13345</t>
+          <t>12721</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10246</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23378</t>
+          <t>22459</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8957</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>13896</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>161631</t>
+          <t>162226</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>175958</t>
+          <t>176503</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>175748</t>
+          <t>176281</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>189552</t>
+          <t>190370</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>341468</t>
+          <t>343764</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>362270</t>
+          <t>362879</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,88%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>16833</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17195</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14658</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30165</t>
+          <t>29774</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15422</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17990</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>14802</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>29325</t>
+          <t>29576</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15176</t>
+          <t>15199</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30062</t>
+          <t>30279</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15723</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31025</t>
+          <t>31347</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>35027</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>56926</t>
+          <t>56302</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10674</t>
+          <t>10147</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>23544</t>
+          <t>23076</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16435</t>
+          <t>16138</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>35064</t>
+          <t>35507</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>559438</t>
+          <t>559304</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>582590</t>
+          <t>583117</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>603004</t>
+          <t>605200</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>626989</t>
+          <t>627636</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1171440</t>
+          <t>1170816</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1204376</t>
+          <t>1205037</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>496</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>573</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>583</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78188</t>
+          <t>78167</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84293</t>
+          <t>84303</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78622</t>
+          <t>78601</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84073</t>
+          <t>84071</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>159517</t>
+          <t>159543</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>167209</t>
+          <t>167349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7272</t>
+          <t>6900</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>693</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6124</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17773</t>
+          <t>18063</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>846</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13696</t>
+          <t>13315</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214515</t>
+          <t>213870</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>226895</t>
+          <t>226801</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>245305</t>
+          <t>246438</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>258371</t>
+          <t>258527</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>465296</t>
+          <t>465406</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>482536</t>
+          <t>483303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12510</t>
+          <t>12862</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>776</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>770</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7454</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>10577</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,47 +5979,47 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4313</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>9181</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
           <t>1,26%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>4313</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1537</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>9210</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5044</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14562</t>
+          <t>15228</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>11248</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17578</t>
+          <t>17975</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>129299</t>
+          <t>131379</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>143845</t>
+          <t>143789</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>134303</t>
+          <t>134109</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>147265</t>
+          <t>146744</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>270653</t>
+          <t>269185</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>287974</t>
+          <t>287979</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11142</t>
+          <t>11563</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>613</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13726</t>
+          <t>14099</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10041</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12758</t>
+          <t>12370</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9552</t>
+          <t>9728</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18886</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10012</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16499</t>
+          <t>16940</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>137973</t>
+          <t>138137</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>152267</t>
+          <t>152685</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>156027</t>
+          <t>155697</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>167610</t>
+          <t>166670</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>298279</t>
+          <t>298344</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>317614</t>
+          <t>316337</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>17729</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16877</t>
+          <t>17008</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15127</t>
+          <t>15403</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30544</t>
+          <t>31621</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17839</t>
+          <t>19082</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>11511</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>25185</t>
+          <t>26232</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13442</t>
+          <t>13869</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28881</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19601</t>
+          <t>19213</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>24453</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>42022</t>
+          <t>41717</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>10559</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>23898</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>23723</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>24521</t>
+          <t>24440</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>41306</t>
+          <t>43976</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>574966</t>
+          <t>574626</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>599087</t>
+          <t>598841</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>626745</t>
+          <t>625489</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>648759</t>
+          <t>648376</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1209548</t>
+          <t>1209752</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1241066</t>
+          <t>1241410</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>2716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>617</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7263</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70784</t>
+          <t>70962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77732</t>
+          <t>77865</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64324</t>
+          <t>64910</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72372</t>
+          <t>72666</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>138397</t>
+          <t>138312</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>148503</t>
+          <t>148957</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -8811,82 +8811,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5261</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
           <t>573</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5372</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1940</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9609</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14216</t>
+          <t>14363</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9016</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>6444</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16859</t>
+          <t>17883</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22379</t>
+          <t>23059</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189409</t>
+          <t>188482</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>199686</t>
+          <t>199555</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>229650</t>
+          <t>229629</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>241860</t>
+          <t>241790</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>423072</t>
+          <t>422964</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>438410</t>
+          <t>438671</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9086</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>838</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14488</t>
+          <t>14063</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12482</t>
+          <t>12218</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>7393</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18944</t>
+          <t>18324</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>162712</t>
+          <t>163416</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>173961</t>
+          <t>174118</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>161280</t>
+          <t>161130</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>173809</t>
+          <t>173919</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>328868</t>
+          <t>329340</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>345596</t>
+          <t>345461</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,61%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10384</t>
+          <t>10085</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11187</t>
+          <t>10753</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11327</t>
+          <t>11689</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,82 +10303,82 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>4284</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>1958</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>9358</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>10141</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>5192</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>16192</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>1,53%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>4284</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>1571</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>8801</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>10141</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>5637</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>16457</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19392</t>
+          <t>19922</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>15097</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15167</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30819</t>
+          <t>30437</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>136888</t>
+          <t>136867</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>152845</t>
+          <t>152101</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>146911</t>
+          <t>146232</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>159813</t>
+          <t>159221</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>287403</t>
+          <t>288240</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>308458</t>
+          <t>310320</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14023</t>
+          <t>14286</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7191</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18890</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8407</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23939</t>
+          <t>23417</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22343</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>22460</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>40098</t>
+          <t>39584</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>17419</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>34231</t>
+          <t>32914</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>22016</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>39425</t>
+          <t>39809</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>43914</t>
+          <t>43572</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>65989</t>
+          <t>69069</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>571879</t>
+          <t>572041</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>594843</t>
+          <t>595494</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>615182</t>
+          <t>614476</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>638261</t>
+          <t>638464</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1196092</t>
+          <t>1194613</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1228129</t>
+          <t>1227350</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
